--- a/artfynd/A 49335-2024 artfynd.xlsx
+++ b/artfynd/A 49335-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120900042</v>
+        <v>120899878</v>
       </c>
       <c r="B2" t="n">
-        <v>91127</v>
+        <v>91137</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,17 +708,26 @@
           <t>P.Karst.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilla Efrikgården, Falun, Lilla Efrikgården, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533985</v>
+        <v>533966</v>
       </c>
       <c r="R2" t="n">
-        <v>6727096</v>
+        <v>6727073</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +799,7 @@
         <v>120899943</v>
       </c>
       <c r="B3" t="n">
-        <v>90973</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120899878</v>
+        <v>120900042</v>
       </c>
       <c r="B4" t="n">
-        <v>91127</v>
+        <v>91137</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,26 +941,17 @@
           <t>P.Karst.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilla Efrikgården, Falun, Lilla Efrikgården, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533966</v>
+        <v>533985</v>
       </c>
       <c r="R4" t="n">
-        <v>6727073</v>
+        <v>6727096</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 49335-2024 artfynd.xlsx
+++ b/artfynd/A 49335-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120899878</v>
+        <v>120899943</v>
       </c>
       <c r="B2" t="n">
-        <v>91137</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilla Efrikgården, Falun, Lilla Efrikgården, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533966</v>
+        <v>533985</v>
       </c>
       <c r="R2" t="n">
-        <v>6727073</v>
+        <v>6727096</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120899943</v>
+        <v>120900042</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>91137</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -908,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120900042</v>
+        <v>120899878</v>
       </c>
       <c r="B4" t="n">
         <v>91137</v>
@@ -941,17 +932,26 @@
           <t>P.Karst.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilla Efrikgården, Falun, Lilla Efrikgården, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533985</v>
+        <v>533966</v>
       </c>
       <c r="R4" t="n">
-        <v>6727096</v>
+        <v>6727073</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 49335-2024 artfynd.xlsx
+++ b/artfynd/A 49335-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120899943</v>
+        <v>120899878</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>91149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilla Efrikgården, Falun, Lilla Efrikgården, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533985</v>
+        <v>533966</v>
       </c>
       <c r="R2" t="n">
-        <v>6727096</v>
+        <v>6727073</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120900042</v>
+        <v>120899943</v>
       </c>
       <c r="B3" t="n">
-        <v>91137</v>
+        <v>90995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120899878</v>
+        <v>120900042</v>
       </c>
       <c r="B4" t="n">
-        <v>91137</v>
+        <v>91149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,26 +941,17 @@
           <t>P.Karst.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilla Efrikgården, Falun, Lilla Efrikgården, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533966</v>
+        <v>533985</v>
       </c>
       <c r="R4" t="n">
-        <v>6727073</v>
+        <v>6727096</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
